--- a/salidas/empresas/ABT.xlsx
+++ b/salidas/empresas/ABT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.92763233184814</v>
+        <v>12.92763614654541</v>
       </c>
       <c r="C2" t="n">
         <v>20.703369140625</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.23621940612793</v>
+        <v>13.23622131347656</v>
       </c>
       <c r="C3" t="n">
         <v>21.19756317138672</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.72390460968018</v>
+        <v>12.72390365600586</v>
       </c>
       <c r="C4" t="n">
         <v>20.37710571289062</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.89498805999756</v>
+        <v>12.89498615264893</v>
       </c>
       <c r="C5" t="n">
         <v>20.50665283203125</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.8829174041748</v>
+        <v>12.88291358947754</v>
       </c>
       <c r="C6" t="n">
         <v>20.48745918273926</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.15746879577637</v>
+        <v>13.157470703125</v>
       </c>
       <c r="C7" t="n">
         <v>20.9240779876709</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>14.50862693786621</v>
+        <v>14.50862598419189</v>
       </c>
       <c r="C8" t="n">
         <v>22.92004585266113</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.74856472015381</v>
+        <v>14.74856281280518</v>
       </c>
       <c r="C10" t="n">
         <v>23.29908752441406</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.52168464660645</v>
+        <v>14.52168750762939</v>
       </c>
       <c r="C11" t="n">
         <v>22.79529762268066</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.26187992095947</v>
+        <v>14.26187896728516</v>
       </c>
       <c r="C12" t="n">
         <v>22.3874683380127</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>16.29488563537598</v>
+        <v>16.29488372802734</v>
       </c>
       <c r="C14" t="n">
         <v>25.42939949035645</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>16.7929515838623</v>
+        <v>16.79296112060547</v>
       </c>
       <c r="C15" t="n">
         <v>26.2066764831543</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>17.15574836730957</v>
+        <v>17.1557445526123</v>
       </c>
       <c r="C16" t="n">
         <v>26.77284049987793</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>17.4240837097168</v>
+        <v>17.42408752441406</v>
       </c>
       <c r="C18" t="n">
         <v>27.03672981262207</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.55829620361328</v>
+        <v>16.55829429626465</v>
       </c>
       <c r="C19" t="n">
         <v>25.69329071044922</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.77080249786377</v>
+        <v>15.77080154418945</v>
       </c>
       <c r="C20" t="n">
         <v>24.3210620880127</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>16.1503791809082</v>
+        <v>16.15036964416504</v>
       </c>
       <c r="C21" t="n">
         <v>24.90641784667969</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.6823902130127</v>
+        <v>16.68239784240723</v>
       </c>
       <c r="C22" t="n">
         <v>25.72687530517578</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.095947265625</v>
+        <v>17.0959529876709</v>
       </c>
       <c r="C23" t="n">
         <v>26.2066764831543</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>18.00051498413086</v>
+        <v>18.00051879882812</v>
       </c>
       <c r="C24" t="n">
         <v>27.59329795837402</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.57483673095703</v>
+        <v>17.57483863830566</v>
       </c>
       <c r="C25" t="n">
         <v>26.94076919555664</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>17.6798210144043</v>
+        <v>17.67981719970703</v>
       </c>
       <c r="C26" t="n">
         <v>26.95516395568848</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.8521556854248</v>
+        <v>16.85215377807617</v>
       </c>
       <c r="C27" t="n">
         <v>25.69329071044922</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.35568046569824</v>
+        <v>17.35568237304688</v>
       </c>
       <c r="C28" t="n">
         <v>26.46096992492676</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.71199417114258</v>
+        <v>16.71199226379395</v>
       </c>
       <c r="C29" t="n">
         <v>25.30945014953613</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.85253715515137</v>
+        <v>17.8525333404541</v>
       </c>
       <c r="C30" t="n">
         <v>27.03672981262207</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.78170585632324</v>
+        <v>16.78170204162598</v>
       </c>
       <c r="C31" t="n">
         <v>25.41500663757324</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.96211433410645</v>
+        <v>17.96212387084961</v>
       </c>
       <c r="C32" t="n">
         <v>27.03193283081055</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>18.35745239257812</v>
+        <v>18.35745048522949</v>
       </c>
       <c r="C34" t="n">
         <v>27.62688446044922</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>17.7096004486084</v>
+        <v>17.70959854125977</v>
       </c>
       <c r="C35" t="n">
         <v>26.46096992492676</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>16.82331085205078</v>
+        <v>16.82331657409668</v>
       </c>
       <c r="C36" t="n">
         <v>25.13672256469727</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>17.13801765441895</v>
+        <v>17.13801193237305</v>
       </c>
       <c r="C37" t="n">
         <v>25.60692596435547</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.93167686462402</v>
+        <v>17.93168067932129</v>
       </c>
       <c r="C38" t="n">
         <v>26.60011291503906</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.31179523468018</v>
+        <v>15.31178760528564</v>
       </c>
       <c r="C39" t="n">
         <v>22.71373176574707</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.42823028564453</v>
+        <v>15.42823505401611</v>
       </c>
       <c r="C40" t="n">
         <v>22.88645935058594</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.66018390655518</v>
+        <v>13.66018295288086</v>
       </c>
       <c r="C41" t="n">
         <v>20.07962989807129</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.70795249938965</v>
+        <v>14.70796012878418</v>
       </c>
       <c r="C42" t="n">
         <v>21.61978721618652</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.35424518585205</v>
+        <v>15.35424709320068</v>
       </c>
       <c r="C43" t="n">
         <v>22.56979179382324</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>14.89464950561523</v>
+        <v>14.89464569091797</v>
       </c>
       <c r="C45" t="n">
         <v>21.70135307312012</v>
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.08876419067383</v>
+        <v>18.08876800537109</v>
       </c>
       <c r="C48" t="n">
         <v>26.14430236816406</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.92278289794922</v>
+        <v>17.92277526855469</v>
       </c>
       <c r="C49" t="n">
         <v>25.9044017791748</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>17.70256805419922</v>
+        <v>17.70256614685059</v>
       </c>
       <c r="C50" t="n">
         <v>25.40061187744141</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>18.1506519317627</v>
+        <v>18.15064811706543</v>
       </c>
       <c r="C51" t="n">
         <v>26.04354476928711</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.61562347412109</v>
+        <v>17.61562538146973</v>
       </c>
       <c r="C52" t="n">
         <v>25.27586364746094</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.25147247314453</v>
+        <v>17.25147438049316</v>
       </c>
       <c r="C53" t="n">
         <v>24.54656791687012</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.03753089904785</v>
+        <v>16.03753280639648</v>
       </c>
       <c r="C54" t="n">
         <v>22.81928825378418</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>15.77451038360596</v>
+        <v>15.77450847625732</v>
       </c>
       <c r="C55" t="n">
         <v>22.44504356384277</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>16.70377922058105</v>
+        <v>16.70377159118652</v>
       </c>
       <c r="C56" t="n">
         <v>23.548583984375</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>16.7922534942627</v>
+        <v>16.79225921630859</v>
       </c>
       <c r="C57" t="n">
         <v>23.67333221435547</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.77923965454102</v>
+        <v>17.77924728393555</v>
       </c>
       <c r="C58" t="n">
         <v>25.06475257873535</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.61093521118164</v>
+        <v>17.61094093322754</v>
       </c>
       <c r="C59" t="n">
         <v>24.62333679199219</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>15.96034049987793</v>
+        <v>15.96034145355225</v>
       </c>
       <c r="C60" t="n">
         <v>22.31549835205078</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>16.44076156616211</v>
+        <v>16.44076919555664</v>
       </c>
       <c r="C61" t="n">
         <v>22.98721885681152</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>15.64093112945557</v>
+        <v>15.64092826843262</v>
       </c>
       <c r="C62" t="n">
         <v>21.66776847839355</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>16.65918731689453</v>
+        <v>16.65918159484863</v>
       </c>
       <c r="C63" t="n">
         <v>23.0783805847168</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98821067810059</v>
+        <v>16.98821258544922</v>
       </c>
       <c r="C64" t="n">
         <v>23.53418922424316</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>18.19493293762207</v>
+        <v>18.1949348449707</v>
       </c>
       <c r="C65" t="n">
         <v>24.96879196166992</v>
@@ -1836,7 +1848,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1865,7 +1877,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>18.10628128051758</v>
+        <v>18.10627937316895</v>
       </c>
       <c r="C68" t="n">
         <v>24.62333679199219</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>18.52612495422363</v>
+        <v>18.52613639831543</v>
       </c>
       <c r="C69" t="n">
         <v>25.19429779052734</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.04277801513672</v>
+        <v>18.04277610778809</v>
       </c>
       <c r="C70" t="n">
         <v>24.53697204589844</v>
@@ -1981,7 +1993,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2010,7 +2022,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.02094078063965</v>
+        <v>20.02093887329102</v>
       </c>
       <c r="C73" t="n">
         <v>26.97915458679199</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>19.44670867919922</v>
+        <v>19.44671058654785</v>
       </c>
       <c r="C74" t="n">
         <v>25.98117065429688</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>20.33015823364258</v>
+        <v>20.33016395568848</v>
       </c>
       <c r="C75" t="n">
         <v>27.16147804260254</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.0108757019043</v>
+        <v>22.01086807250977</v>
       </c>
       <c r="C76" t="n">
         <v>29.40694236755371</v>
@@ -2155,7 +2167,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.38022422790527</v>
+        <v>22.38022041320801</v>
       </c>
       <c r="C78" t="n">
         <v>29.64684104919434</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>23.35092163085938</v>
+        <v>23.35091209411621</v>
       </c>
       <c r="C79" t="n">
         <v>30.93270683288574</v>
@@ -2242,7 +2254,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>23.92427062988281</v>
+        <v>23.92426300048828</v>
       </c>
       <c r="C81" t="n">
         <v>31.44609260559082</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.02666854858398</v>
+        <v>25.02666664123535</v>
       </c>
       <c r="C82" t="n">
         <v>32.89508819580078</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>24.08421897888184</v>
+        <v>24.08421325683594</v>
       </c>
       <c r="C83" t="n">
         <v>31.42690086364746</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>23.90036201477051</v>
+        <v>23.90036392211914</v>
       </c>
       <c r="C84" t="n">
         <v>31.1870002746582</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.08421897888184</v>
+        <v>24.08421325683594</v>
       </c>
       <c r="C85" t="n">
         <v>31.42690086364746</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.07199859619141</v>
+        <v>26.07199478149414</v>
       </c>
       <c r="C86" t="n">
         <v>33.88000106811523</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>26.00273895263672</v>
+        <v>26.00274085998535</v>
       </c>
       <c r="C87" t="n">
         <v>33.79000091552734</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>27.18013381958008</v>
+        <v>27.18014335632324</v>
       </c>
       <c r="C88" t="n">
         <v>35.31999969482422</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>28.51902008056641</v>
+        <v>28.51901245117188</v>
       </c>
       <c r="C89" t="n">
         <v>36.91999816894531</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>28.32590293884277</v>
+        <v>28.32588958740234</v>
       </c>
       <c r="C90" t="n">
         <v>36.66999816894531</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.94320869445801</v>
+        <v>26.94320678710938</v>
       </c>
       <c r="C91" t="n">
         <v>34.88000106811523</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>28.40949630737305</v>
+        <v>28.40947914123535</v>
       </c>
       <c r="C92" t="n">
         <v>36.63000106811523</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>25.85007095336914</v>
+        <v>25.85007476806641</v>
       </c>
       <c r="C93" t="n">
         <v>33.33000183105469</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>25.74149703979492</v>
+        <v>25.74148750305176</v>
       </c>
       <c r="C94" t="n">
         <v>33.18999862670898</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>28.46760368347168</v>
+        <v>28.46758842468262</v>
       </c>
       <c r="C95" t="n">
         <v>36.54999923706055</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.74494361877441</v>
+        <v>29.74493980407715</v>
       </c>
       <c r="C96" t="n">
         <v>38.18999862670898</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>29.85397148132324</v>
+        <v>29.85396766662598</v>
       </c>
       <c r="C97" t="n">
         <v>38.33000183105469</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>28.71291160583496</v>
+        <v>28.7129020690918</v>
       </c>
       <c r="C98" t="n">
         <v>36.65999984741211</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>31.15655708312988</v>
+        <v>31.15654945373535</v>
       </c>
       <c r="C99" t="n">
         <v>39.77999877929688</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>30.16187477111816</v>
+        <v>30.161865234375</v>
       </c>
       <c r="C100" t="n">
         <v>38.5099983215332</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>31.52281761169434</v>
+        <v>31.52280807495117</v>
       </c>
       <c r="C102" t="n">
         <v>40.0099983215332</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.22403717041016</v>
+        <v>32.22404861450195</v>
       </c>
       <c r="C103" t="n">
         <v>40.90000152587891</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.36321640014648</v>
+        <v>33.36321258544922</v>
       </c>
       <c r="C104" t="n">
         <v>42.11999893188477</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>33.45827102661133</v>
+        <v>33.45827865600586</v>
       </c>
       <c r="C105" t="n">
         <v>42.2400016784668</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.94340896606445</v>
+        <v>32.94340515136719</v>
       </c>
       <c r="C106" t="n">
         <v>41.59000015258789</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>34.71102905273438</v>
+        <v>34.71103668212891</v>
       </c>
       <c r="C107" t="n">
         <v>43.59000015258789</v>
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>35.83138275146484</v>
+        <v>35.83139038085938</v>
       </c>
       <c r="C110" t="n">
         <v>44.7599983215332</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>37.92075347900391</v>
+        <v>37.92075729370117</v>
       </c>
       <c r="C111" t="n">
         <v>47.36999893188477</v>
@@ -3170,7 +3182,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3199,7 +3211,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>39.10444641113281</v>
+        <v>39.10444259643555</v>
       </c>
       <c r="C114" t="n">
         <v>48.59999847412109</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>39.49065399169922</v>
+        <v>39.49066162109375</v>
       </c>
       <c r="C115" t="n">
         <v>49.08000183105469</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>40.98308563232422</v>
+        <v>40.98309326171875</v>
       </c>
       <c r="C116" t="n">
         <v>50.68999862670898</v>
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>32.51803588867188</v>
+        <v>32.51804733276367</v>
       </c>
       <c r="C118" t="n">
         <v>40.22000122070312</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>36.43131637573242</v>
+        <v>36.43132781982422</v>
       </c>
       <c r="C119" t="n">
         <v>44.79999923706055</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>36.52891540527344</v>
+        <v>36.52890396118164</v>
       </c>
       <c r="C120" t="n">
         <v>44.91999816894531</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>36.52077865600586</v>
+        <v>36.52078247070312</v>
       </c>
       <c r="C121" t="n">
         <v>44.90999984741211</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>30.97383499145508</v>
+        <v>30.97383117675781</v>
       </c>
       <c r="C122" t="n">
         <v>37.84999847412109</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>31.7021427154541</v>
+        <v>31.70214080810547</v>
       </c>
       <c r="C123" t="n">
         <v>38.7400016784668</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>34.23078536987305</v>
+        <v>34.23079299926758</v>
       </c>
       <c r="C124" t="n">
         <v>41.83000183105469</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.02755355834961</v>
+        <v>32.02754592895508</v>
       </c>
       <c r="C125" t="n">
         <v>38.90000152587891</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.62858581542969</v>
+        <v>32.62858200073242</v>
       </c>
       <c r="C126" t="n">
         <v>39.63000106811523</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>32.36511993408203</v>
+        <v>32.36511611938477</v>
       </c>
       <c r="C127" t="n">
         <v>39.31000137329102</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>37.07097625732422</v>
+        <v>37.07096862792969</v>
       </c>
       <c r="C128" t="n">
         <v>44.75</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>34.80945205688477</v>
+        <v>34.80944442749023</v>
       </c>
       <c r="C129" t="n">
         <v>42.02000045776367</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>35.03311538696289</v>
+        <v>35.03311157226562</v>
       </c>
       <c r="C130" t="n">
         <v>42.29000091552734</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>32.71312713623047</v>
+        <v>32.71313095092773</v>
       </c>
       <c r="C131" t="n">
         <v>39.2400016784668</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>31.73773193359375</v>
+        <v>31.73774719238281</v>
       </c>
       <c r="C132" t="n">
         <v>38.06999969482422</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>32.02117538452148</v>
+        <v>32.02118301391602</v>
       </c>
       <c r="C133" t="n">
         <v>38.40999984741211</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.04724502563477</v>
+        <v>35.0472412109375</v>
       </c>
       <c r="C134" t="n">
         <v>41.77000045776367</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>37.82452011108398</v>
+        <v>37.82451248168945</v>
       </c>
       <c r="C135" t="n">
         <v>45.08000183105469</v>
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.84024429321289</v>
+        <v>36.84022903442383</v>
       </c>
       <c r="C137" t="n">
         <v>43.63999938964844</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>38.54549407958984</v>
+        <v>38.54549789428711</v>
       </c>
       <c r="C138" t="n">
         <v>45.65999984741211</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>41.03583145141602</v>
+        <v>41.03582763671875</v>
       </c>
       <c r="C139" t="n">
         <v>48.61000061035156</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.74678421020508</v>
+        <v>41.74677658081055</v>
       </c>
       <c r="C140" t="n">
         <v>49.18000030517578</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>43.24077224731445</v>
+        <v>43.24076843261719</v>
       </c>
       <c r="C141" t="n">
         <v>50.93999862670898</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>45.29500579833984</v>
+        <v>45.29501342773438</v>
       </c>
       <c r="C142" t="n">
         <v>53.36000061035156</v>
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>48.08412933349609</v>
+        <v>48.0841178894043</v>
       </c>
       <c r="C144" t="n">
         <v>56.36999893188477</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>48.68124008178711</v>
+        <v>48.68122482299805</v>
       </c>
       <c r="C145" t="n">
         <v>57.06999969482422</v>
@@ -4156,7 +4168,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>51.70813751220703</v>
+        <v>51.70814514160156</v>
       </c>
       <c r="C147" t="n">
         <v>60.33000183105469</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.35673522949219</v>
+        <v>51.35674667358398</v>
       </c>
       <c r="C148" t="n">
         <v>59.91999816894531</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>50.06237030029297</v>
+        <v>50.0623664855957</v>
       </c>
       <c r="C149" t="n">
         <v>58.13000106811523</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>52.99049758911133</v>
+        <v>52.99049377441406</v>
       </c>
       <c r="C150" t="n">
         <v>61.52999877929688</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>52.52543640136719</v>
+        <v>52.52544403076172</v>
       </c>
       <c r="C151" t="n">
         <v>60.9900016784668</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>56.69770050048828</v>
+        <v>56.69769287109375</v>
       </c>
       <c r="C152" t="n">
         <v>65.54000091552734</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>57.82230377197266</v>
+        <v>57.82231521606445</v>
       </c>
       <c r="C153" t="n">
         <v>66.83999633789062</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>63.462646484375</v>
+        <v>63.46267318725586</v>
       </c>
       <c r="C154" t="n">
         <v>73.36000061035156</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>59.88419342041016</v>
+        <v>59.88418960571289</v>
       </c>
       <c r="C155" t="n">
         <v>68.94000244140625</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>64.32294464111328</v>
+        <v>64.32296752929688</v>
       </c>
       <c r="C156" t="n">
         <v>74.05000305175781</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>62.82891082763672</v>
+        <v>62.82888412475586</v>
       </c>
       <c r="C157" t="n">
         <v>72.33000183105469</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>63.68745040893555</v>
+        <v>63.68746948242188</v>
       </c>
       <c r="C158" t="n">
         <v>72.98000335693359</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>67.73665618896484</v>
+        <v>67.73666381835938</v>
       </c>
       <c r="C159" t="n">
         <v>77.62000274658203</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>69.76126098632812</v>
+        <v>69.76123809814453</v>
       </c>
       <c r="C160" t="n">
         <v>79.94000244140625</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>69.71378326416016</v>
+        <v>69.71377563476562</v>
       </c>
       <c r="C161" t="n">
         <v>79.55999755859375</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>66.70825958251953</v>
+        <v>66.70826721191406</v>
       </c>
       <c r="C162" t="n">
         <v>76.12999725341797</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>73.69190979003906</v>
+        <v>73.69190216064453</v>
       </c>
       <c r="C163" t="n">
         <v>84.09999847412109</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>76.6064453125</v>
+        <v>76.60646057128906</v>
       </c>
       <c r="C164" t="n">
         <v>87.09999847412109</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>75.04090881347656</v>
+        <v>75.04090118408203</v>
       </c>
       <c r="C165" t="n">
         <v>85.31999969482422</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>73.58968353271484</v>
+        <v>73.58967590332031</v>
       </c>
       <c r="C166" t="n">
         <v>83.66999816894531</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>73.83174133300781</v>
+        <v>73.83174896240234</v>
       </c>
       <c r="C167" t="n">
         <v>83.61000061035156</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>75.45652008056641</v>
+        <v>75.45652770996094</v>
       </c>
       <c r="C168" t="n">
         <v>85.44999694824219</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>76.70162963867188</v>
+        <v>76.70164489746094</v>
       </c>
       <c r="C169" t="n">
         <v>86.86000061035156</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>77.27571105957031</v>
+        <v>77.27569580078125</v>
       </c>
       <c r="C170" t="n">
         <v>87.13999938964844</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>68.31017303466797</v>
+        <v>68.31016540527344</v>
       </c>
       <c r="C171" t="n">
         <v>77.02999877929688</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>69.97737121582031</v>
+        <v>69.97734832763672</v>
       </c>
       <c r="C172" t="n">
         <v>78.91000366210938</v>
@@ -4939,7 +4951,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>84.52948760986328</v>
+        <v>84.52946472167969</v>
       </c>
       <c r="C174" t="n">
         <v>94.91999816894531</v>
@@ -4997,11 +5009,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>81.4215087890625</v>
+        <v>81.42149353027344</v>
       </c>
       <c r="C175" t="n">
         <v>91.43000030517578</v>
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>89.97127532958984</v>
+        <v>89.97128295898438</v>
       </c>
       <c r="C176" t="n">
         <v>100.6399993896484</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>97.86520385742188</v>
+        <v>97.86521911621094</v>
       </c>
       <c r="C177" t="n">
         <v>109.4700012207031</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>97.29306793212891</v>
+        <v>97.29306030273438</v>
       </c>
       <c r="C178" t="n">
         <v>108.8300018310547</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>94.28061676025391</v>
+        <v>94.28060913085938</v>
       </c>
       <c r="C179" t="n">
         <v>105.1100006103516</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>97.0701904296875</v>
+        <v>97.07018280029297</v>
       </c>
       <c r="C180" t="n">
         <v>108.2200012207031</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>98.20932769775391</v>
+        <v>98.20933532714844</v>
       </c>
       <c r="C181" t="n">
         <v>109.4899978637695</v>
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>111.3032150268555</v>
+        <v>111.3032302856445</v>
       </c>
       <c r="C182" t="n">
         <v>123.5899963378906</v>
@@ -5229,7 +5241,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>107.9260406494141</v>
+        <v>107.9260330200195</v>
       </c>
       <c r="C184" t="n">
         <v>119.8399963378906</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>108.5392379760742</v>
+        <v>108.5392303466797</v>
       </c>
       <c r="C185" t="n">
         <v>120.0800018310547</v>
@@ -5316,7 +5328,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5345,11 +5357,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>104.7880935668945</v>
+        <v>104.7880859375</v>
       </c>
       <c r="C187" t="n">
         <v>115.9300003051758</v>
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>109.7690582275391</v>
+        <v>109.7690505981445</v>
       </c>
       <c r="C188" t="n">
         <v>120.9800033569336</v>
@@ -5403,7 +5415,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>107.1831665039062</v>
+        <v>107.1831436157227</v>
       </c>
       <c r="C190" t="n">
         <v>118.129997253418</v>
@@ -5461,7 +5473,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5490,11 +5502,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>114.5557708740234</v>
+        <v>114.5557632446289</v>
       </c>
       <c r="C192" t="n">
         <v>125.7699966430664</v>
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>128.1909790039062</v>
+        <v>128.1909942626953</v>
       </c>
       <c r="C193" t="n">
         <v>140.7400054931641</v>
@@ -5548,11 +5560,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>116.5045852661133</v>
+        <v>116.5045776367188</v>
       </c>
       <c r="C194" t="n">
         <v>127.4599990844727</v>
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>110.2525024414062</v>
+        <v>110.2524948120117</v>
       </c>
       <c r="C195" t="n">
         <v>120.620002746582</v>
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>108.1867599487305</v>
+        <v>108.1867370605469</v>
       </c>
       <c r="C196" t="n">
         <v>118.3600006103516</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>104.1579513549805</v>
+        <v>104.1579666137695</v>
       </c>
       <c r="C197" t="n">
         <v>113.5</v>
@@ -5664,7 +5676,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>99.7071533203125</v>
+        <v>99.70716857910156</v>
       </c>
       <c r="C199" t="n">
         <v>108.6500015258789</v>
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>100.3254852294922</v>
+        <v>100.3254623413086</v>
       </c>
       <c r="C200" t="n">
         <v>108.8399963378906</v>
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>94.61972045898438</v>
+        <v>94.61972808837891</v>
       </c>
       <c r="C201" t="n">
         <v>102.6500015258789</v>
@@ -5780,7 +5792,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>99.63193511962891</v>
+        <v>99.63195037841797</v>
       </c>
       <c r="C204" t="n">
         <v>107.5800018310547</v>
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>101.6786880493164</v>
+        <v>101.6786804199219</v>
       </c>
       <c r="C205" t="n">
         <v>109.7900009155273</v>
@@ -5896,7 +5908,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>94.63140869140625</v>
+        <v>94.63140106201172</v>
       </c>
       <c r="C207" t="n">
         <v>101.7200012207031</v>
@@ -5954,7 +5966,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>103.285270690918</v>
+        <v>103.2852630615234</v>
       </c>
       <c r="C209" t="n">
         <v>110.4700012207031</v>
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>95.36612701416016</v>
+        <v>95.36611938476562</v>
       </c>
       <c r="C210" t="n">
         <v>102</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>101.9295654296875</v>
+        <v>101.9295501708984</v>
       </c>
       <c r="C211" t="n">
         <v>109.0199966430664</v>
@@ -6070,7 +6082,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>96.66899871826172</v>
+        <v>96.66900634765625</v>
       </c>
       <c r="C213" t="n">
         <v>102.9000015258789</v>
@@ -6128,7 +6140,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6157,7 +6169,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6186,7 +6198,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6215,7 +6227,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6244,7 +6256,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>112.6142807006836</v>
+        <v>112.6142883300781</v>
       </c>
       <c r="C219" t="n">
         <v>118.6399993896484</v>
@@ -6302,7 +6314,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6331,7 +6343,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6360,11 +6372,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>97.48084259033203</v>
+        <v>97.48085021972656</v>
       </c>
       <c r="C222" t="n">
         <v>102.1900024414062</v>
@@ -6389,11 +6401,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>99.12157440185547</v>
+        <v>99.12158203125</v>
       </c>
       <c r="C223" t="n">
         <v>103.9100036621094</v>
@@ -6418,11 +6430,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>101.5941848754883</v>
+        <v>101.5941772460938</v>
       </c>
       <c r="C224" t="n">
         <v>105.9400024414062</v>
@@ -6447,7 +6459,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6476,11 +6488,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>109.333137512207</v>
+        <v>109.3331298828125</v>
       </c>
       <c r="C226" t="n">
         <v>114.0100021362305</v>
@@ -6505,11 +6517,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>109.2317657470703</v>
+        <v>109.2317733764648</v>
       </c>
       <c r="C227" t="n">
         <v>113.370002746582</v>
@@ -6534,11 +6546,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>114.4346542358398</v>
+        <v>114.4346618652344</v>
       </c>
       <c r="C228" t="n">
         <v>118.7699966430664</v>
@@ -6563,11 +6575,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>108.9812622070312</v>
+        <v>108.9812698364258</v>
       </c>
       <c r="C229" t="n">
         <v>113.1100006103516</v>
@@ -6592,7 +6604,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6621,11 +6633,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>133.6701507568359</v>
+        <v>133.670166015625</v>
       </c>
       <c r="C231" t="n">
         <v>138.0099945068359</v>
@@ -6650,11 +6662,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>128.4786987304688</v>
+        <v>128.4786834716797</v>
       </c>
       <c r="C232" t="n">
         <v>132.6499938964844</v>
@@ -6679,11 +6691,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>127.2250747680664</v>
+        <v>127.2250671386719</v>
       </c>
       <c r="C233" t="n">
         <v>130.75</v>
@@ -6708,7 +6720,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6737,11 +6749,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>132.3432464599609</v>
+        <v>132.34326171875</v>
       </c>
       <c r="C235" t="n">
         <v>136.0099945068359</v>
@@ -6766,11 +6778,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>123.3391723632812</v>
+        <v>123.3391647338867</v>
       </c>
       <c r="C236" t="n">
         <v>126.1900024414062</v>
@@ -6795,11 +6807,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>129.6629943847656</v>
+        <v>129.6630096435547</v>
       </c>
       <c r="C237" t="n">
         <v>132.6600036621094</v>
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>103.4899978637695</v>
+        <v>101.0699996948242</v>
       </c>
       <c r="C250" t="n">
-        <v>103.4899978637695</v>
+        <v>101.0699996948242</v>
       </c>
       <c r="D250" t="n">
-        <v>143648000</v>
+        <v>149864200</v>
       </c>
       <c r="E250" t="n">
         <v>3.089999999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>33.49190869377655</v>
+        <v>32.70873776531528</v>
       </c>
       <c r="G250" t="n">
         <v>1741812429</v>
       </c>
       <c r="H250" t="n">
-        <v>180260164556.2972</v>
+        <v>176044981667.471</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08247041851829615</v>
+        <v>0.08603922988770911</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7450,7 +7462,7 @@
       <c r="I5" t="n">
         <v>1.496976</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K5" t="n">
@@ -7463,13 +7475,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7496,7 +7508,7 @@
       <c r="I6" t="n">
         <v>1.650512</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K6" t="n">
@@ -7509,13 +7521,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7542,7 +7554,7 @@
       <c r="I7" t="n">
         <v>1.640916</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K7" t="n">
@@ -7555,13 +7567,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7588,7 +7600,7 @@
       <c r="I8" t="n">
         <v>1.765664</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K8" t="n">
@@ -7601,13 +7613,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7634,7 +7646,7 @@
       <c r="I9" t="n">
         <v>1.765664</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K9" t="n">
@@ -7647,13 +7659,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7680,7 +7692,7 @@
       <c r="I10" t="n">
         <v>1.63132</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K10" t="n">
@@ -7693,13 +7705,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7726,7 +7738,7 @@
       <c r="I11" t="n">
         <v>1.63132</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K11" t="n">
@@ -7739,13 +7751,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7772,7 +7784,7 @@
       <c r="I12" t="n">
         <v>1.448996</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K12" t="n">
@@ -7785,13 +7797,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7818,7 +7830,7 @@
       <c r="I13" t="n">
         <v>1.420208</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K13" t="n">
@@ -7831,13 +7843,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7864,7 +7876,7 @@
       <c r="I14" t="n">
         <v>1.377026</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K14" t="n">
@@ -7877,13 +7889,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7910,7 +7922,7 @@
       <c r="I15" t="n">
         <v>1.568946</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K15" t="n">
@@ -7923,13 +7935,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7956,7 +7968,7 @@
       <c r="I16" t="n">
         <v>1.386622</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K16" t="n">
@@ -7969,13 +7981,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8002,7 +8014,7 @@
       <c r="I17" t="n">
         <v>1.434602</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K17" t="n">
@@ -8015,13 +8027,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8048,7 +8060,7 @@
       <c r="I18" t="n">
         <v>1.544956</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K18" t="n">
@@ -8061,13 +8073,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8094,7 +8106,7 @@
       <c r="I19" t="n">
         <v>1.472986</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K19" t="n">
@@ -8107,13 +8119,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8140,7 +8152,7 @@
       <c r="I20" t="n">
         <v>1.962382</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K20" t="n">
@@ -8153,13 +8165,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8186,7 +8198,7 @@
       <c r="I21" t="n">
         <v>2.132986</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K21" t="n">
@@ -8199,13 +8211,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8232,7 +8244,7 @@
       <c r="I22" t="n">
         <v>2.098742</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K22" t="n">
@@ -8245,13 +8257,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8278,7 +8290,7 @@
       <c r="I23" t="n">
         <v>1.880558</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K23" t="n">
@@ -8291,13 +8303,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8324,7 +8336,7 @@
       <c r="I24" t="n">
         <v>1.91</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K24" t="n">
@@ -8337,13 +8349,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8370,7 +8382,7 @@
       <c r="I25" t="n">
         <v>1.62</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K25" t="n">
@@ -8383,13 +8395,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8416,7 +8428,7 @@
       <c r="I26" t="n">
         <v>1.52</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K26" t="n">
@@ -8429,13 +8441,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8462,7 +8474,7 @@
       <c r="I27" t="n">
         <v>1.52</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K27" t="n">
@@ -8475,13 +8487,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8508,7 +8520,7 @@
       <c r="I28" t="n">
         <v>1.27</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K28" t="n">
@@ -8521,13 +8533,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8554,7 +8566,7 @@
       <c r="I29" t="n">
         <v>1.49</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K29" t="n">
@@ -8567,13 +8579,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8600,7 +8612,7 @@
       <c r="I30" t="n">
         <v>2.76</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K30" t="n">
@@ -8613,13 +8625,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8646,7 +8658,7 @@
       <c r="I31" t="n">
         <v>2.98</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K31" t="n">
@@ -8659,13 +8671,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8692,7 +8704,7 @@
       <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K32" t="n">
@@ -8705,13 +8717,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8738,7 +8750,7 @@
       <c r="I33" t="n">
         <v>2.919999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K33" t="n">
@@ -8751,13 +8763,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8784,7 +8796,7 @@
       <c r="I34" t="n">
         <v>1.62</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K34" t="n">
@@ -8797,13 +8809,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8830,7 +8842,7 @@
       <c r="I35" t="n">
         <v>1.51</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K35" t="n">
@@ -8843,13 +8855,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8876,7 +8888,7 @@
       <c r="I36" t="n">
         <v>0.9099999999999995</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K36" t="n">
@@ -8889,13 +8901,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8922,7 +8934,7 @@
       <c r="I37" t="n">
         <v>0.9299999999999996</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K37" t="n">
@@ -8935,13 +8947,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8968,7 +8980,7 @@
       <c r="I38" t="n">
         <v>0.9599999999999996</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K38" t="n">
@@ -8981,13 +8993,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9014,7 +9026,7 @@
       <c r="I39" t="n">
         <v>0.7099999999999996</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K39" t="n">
@@ -9027,13 +9039,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9060,7 +9072,7 @@
       <c r="I40" t="n">
         <v>1.27</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K40" t="n">
@@ -9073,13 +9085,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9106,7 +9118,7 @@
       <c r="I41" t="n">
         <v>0.2599999999999996</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K41" t="n">
@@ -9119,13 +9131,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9152,7 +9164,7 @@
       <c r="I42" t="n">
         <v>0.2499999999999996</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K42" t="n">
@@ -9165,13 +9177,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9198,7 +9210,7 @@
       <c r="I43" t="n">
         <v>0.4999999999999996</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K43" t="n">
@@ -9211,13 +9223,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9244,7 +9256,7 @@
       <c r="I44" t="n">
         <v>0.4799999999999995</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K44" t="n">
@@ -9257,13 +9269,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9290,7 +9302,7 @@
       <c r="I45" t="n">
         <v>1.33</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K45" t="n">
@@ -9303,13 +9315,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9336,7 +9348,7 @@
       <c r="I46" t="n">
         <v>1.48</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K46" t="n">
@@ -9349,13 +9361,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9382,7 +9394,7 @@
       <c r="I47" t="n">
         <v>1.629999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K47" t="n">
@@ -9395,13 +9407,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9428,7 +9440,7 @@
       <c r="I48" t="n">
         <v>1.84</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K48" t="n">
@@ -9441,13 +9453,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9474,7 +9486,7 @@
       <c r="I49" t="n">
         <v>2.06</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K49" t="n">
@@ -9487,13 +9499,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9520,7 +9532,7 @@
       <c r="I50" t="n">
         <v>1.99</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K50" t="n">
@@ -9533,13 +9545,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9566,7 +9578,7 @@
       <c r="I51" t="n">
         <v>1.73</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K51" t="n">
@@ -9579,13 +9591,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9612,7 +9624,7 @@
       <c r="I52" t="n">
         <v>1.889999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K52" t="n">
@@ -9625,13 +9637,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9658,7 +9670,7 @@
       <c r="I53" t="n">
         <v>2.5</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="K53" t="n">
@@ -9671,13 +9683,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9704,7 +9716,7 @@
       <c r="I54" t="n">
         <v>3.19</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K54" t="n">
@@ -9717,13 +9729,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9750,7 +9762,7 @@
       <c r="I55" t="n">
         <v>3.55</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K55" t="n">
@@ -9763,13 +9775,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9796,7 +9808,7 @@
       <c r="I56" t="n">
         <v>4.029999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K56" t="n">
@@ -9809,13 +9821,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9842,7 +9854,7 @@
       <c r="I57" t="n">
         <v>3.94</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="K57" t="n">
@@ -9855,13 +9867,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9888,7 +9900,7 @@
       <c r="I58" t="n">
         <v>4.31</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K58" t="n">
@@ -9901,13 +9913,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9934,7 +9946,7 @@
       <c r="I59" t="n">
         <v>4.789999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K59" t="n">
@@ -9947,13 +9959,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9980,7 +9992,7 @@
       <c r="I60" t="n">
         <v>4.43</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K60" t="n">
@@ -9993,13 +10005,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10026,7 +10038,7 @@
       <c r="I61" t="n">
         <v>3.91</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="K61" t="n">
@@ -10039,13 +10051,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10072,7 +10084,7 @@
       <c r="I62" t="n">
         <v>3.29</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K62" t="n">
@@ -10085,13 +10097,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10118,7 +10130,7 @@
       <c r="I63" t="n">
         <v>2.93</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K63" t="n">
@@ -10131,13 +10143,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10164,7 +10176,7 @@
       <c r="I64" t="n">
         <v>2.94</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K64" t="n">
@@ -10177,13 +10189,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10210,7 +10222,7 @@
       <c r="I65" t="n">
         <v>3.259999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K65" t="n">
@@ -10223,13 +10235,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10256,7 +10268,7 @@
       <c r="I66" t="n">
         <v>3.209999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K66" t="n">
@@ -10269,13 +10281,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10302,7 +10314,7 @@
       <c r="I67" t="n">
         <v>3.169999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K67" t="n">
@@ -10315,13 +10327,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10348,7 +10360,7 @@
       <c r="I68" t="n">
         <v>3.289999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K68" t="n">
@@ -10361,13 +10373,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10394,7 +10406,7 @@
       <c r="I69" t="n">
         <v>7.639999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K69" t="n">
@@ -10407,13 +10419,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10440,7 +10452,7 @@
       <c r="I70" t="n">
         <v>7.699999999999998</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K70" t="n">
@@ -10453,13 +10465,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10486,7 +10498,7 @@
       <c r="I71" t="n">
         <v>7.969999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K71" t="n">
@@ -10499,13 +10511,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10532,7 +10544,7 @@
       <c r="I72" t="n">
         <v>7.969999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K72" t="n">
@@ -10545,13 +10557,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10578,7 +10590,7 @@
       <c r="I73" t="n">
         <v>3.719999999999999</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K73" t="n">
@@ -10591,13 +10603,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10624,7 +10636,7 @@
       <c r="I74" t="n">
         <v>3.569999999999999</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K74" t="n">
@@ -10637,13 +10649,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10664,7 +10676,7 @@
       <c r="I75" t="n">
         <v>3.089999999999999</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K75" t="n">
@@ -10701,52 +10713,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="C4" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C5" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C8" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="C12" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C14" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C15" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="C16" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C19" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C20" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C21" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C23" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C24" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C27" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C28" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C32" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C35" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C36" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C38" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C39" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C40" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C43" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C44" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C47" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="C48" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="C52" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C53" t="n">
@@ -12407,10 +12419,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C54" t="n">
@@ -12439,10 +12451,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C55" t="n">
@@ -12471,10 +12483,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="C56" t="n">
@@ -12503,10 +12515,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C57" t="n">
@@ -12535,10 +12547,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12567,10 +12579,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C59" t="n">
@@ -12599,10 +12611,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C60" t="n">
@@ -12631,10 +12643,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12663,10 +12675,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C62" t="n">
@@ -12695,10 +12707,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12727,10 +12739,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C64" t="n">
@@ -12759,10 +12771,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C65" t="n">
@@ -12791,10 +12803,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C66" t="n">
@@ -12823,10 +12835,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C67" t="n">
@@ -12855,10 +12867,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C68" t="n">
@@ -12887,10 +12899,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C69" t="n">
@@ -12937,12 +12949,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/ABT.xlsx
+++ b/salidas/empresas/ABT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.92763614654541</v>
+        <v>12.92763328552246</v>
       </c>
       <c r="C2" t="n">
         <v>20.703369140625</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.23622131347656</v>
+        <v>13.23621940612793</v>
       </c>
       <c r="C3" t="n">
         <v>21.19756317138672</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.72390365600586</v>
+        <v>12.72390747070312</v>
       </c>
       <c r="C4" t="n">
         <v>20.37710571289062</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.89498615264893</v>
+        <v>12.89498329162598</v>
       </c>
       <c r="C5" t="n">
         <v>20.50665283203125</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.157470703125</v>
+        <v>13.15746688842773</v>
       </c>
       <c r="C7" t="n">
         <v>20.9240779876709</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>14.50862598419189</v>
+        <v>14.50862312316895</v>
       </c>
       <c r="C8" t="n">
         <v>22.92004585266113</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.74856281280518</v>
+        <v>14.74855899810791</v>
       </c>
       <c r="C10" t="n">
         <v>23.29908752441406</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>14.88847160339355</v>
+        <v>14.88846969604492</v>
       </c>
       <c r="C13" t="n">
         <v>23.37105751037598</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>16.79296112060547</v>
+        <v>16.79295349121094</v>
       </c>
       <c r="C15" t="n">
         <v>26.2066764831543</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>17.1557445526123</v>
+        <v>17.15574645996094</v>
       </c>
       <c r="C16" t="n">
         <v>26.77284049987793</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>17.5075740814209</v>
+        <v>17.50757789611816</v>
       </c>
       <c r="C17" t="n">
         <v>27.1662769317627</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>17.42408752441406</v>
+        <v>17.42408180236816</v>
       </c>
       <c r="C18" t="n">
         <v>27.03672981262207</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.55829429626465</v>
+        <v>16.55829620361328</v>
       </c>
       <c r="C19" t="n">
         <v>25.69329071044922</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.77080154418945</v>
+        <v>15.7707986831665</v>
       </c>
       <c r="C20" t="n">
         <v>24.3210620880127</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>16.15036964416504</v>
+        <v>16.1503734588623</v>
       </c>
       <c r="C21" t="n">
         <v>24.90641784667969</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.68239784240723</v>
+        <v>16.68239212036133</v>
       </c>
       <c r="C22" t="n">
         <v>25.72687530517578</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>18.00051879882812</v>
+        <v>18.00051307678223</v>
       </c>
       <c r="C24" t="n">
         <v>27.59329795837402</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.57483863830566</v>
+        <v>17.5748405456543</v>
       </c>
       <c r="C25" t="n">
         <v>26.94076919555664</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>17.67981719970703</v>
+        <v>17.67982292175293</v>
       </c>
       <c r="C26" t="n">
         <v>26.95516395568848</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.85215377807617</v>
+        <v>16.85215759277344</v>
       </c>
       <c r="C27" t="n">
         <v>25.69329071044922</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.71199226379395</v>
+        <v>16.71200561523438</v>
       </c>
       <c r="C29" t="n">
         <v>25.30945014953613</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.8525333404541</v>
+        <v>17.85253143310547</v>
       </c>
       <c r="C30" t="n">
         <v>27.03672981262207</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.78170204162598</v>
+        <v>16.78169631958008</v>
       </c>
       <c r="C31" t="n">
         <v>25.41500663757324</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.96212387084961</v>
+        <v>17.96211624145508</v>
       </c>
       <c r="C32" t="n">
         <v>27.03193283081055</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>18.35745048522949</v>
+        <v>18.35744667053223</v>
       </c>
       <c r="C34" t="n">
         <v>27.62688446044922</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>17.13801193237305</v>
+        <v>17.13800621032715</v>
       </c>
       <c r="C37" t="n">
         <v>25.60692596435547</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.93168067932129</v>
+        <v>17.93166923522949</v>
       </c>
       <c r="C38" t="n">
         <v>26.60011291503906</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.31178760528564</v>
+        <v>15.31178569793701</v>
       </c>
       <c r="C39" t="n">
         <v>22.71373176574707</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.42823505401611</v>
+        <v>15.42822933197021</v>
       </c>
       <c r="C40" t="n">
         <v>22.88645935058594</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.66018295288086</v>
+        <v>13.66018486022949</v>
       </c>
       <c r="C41" t="n">
         <v>20.07962989807129</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.70796012878418</v>
+        <v>14.70796489715576</v>
       </c>
       <c r="C42" t="n">
         <v>21.61978721618652</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.35424709320068</v>
+        <v>15.35424900054932</v>
       </c>
       <c r="C43" t="n">
         <v>22.56979179382324</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>16.29091835021973</v>
+        <v>16.29092025756836</v>
       </c>
       <c r="C46" t="n">
         <v>23.7357063293457</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.78746032714844</v>
+        <v>16.78745460510254</v>
       </c>
       <c r="C47" t="n">
         <v>24.26348686218262</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.08876800537109</v>
+        <v>18.08876419067383</v>
       </c>
       <c r="C48" t="n">
         <v>26.14430236816406</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.92277526855469</v>
+        <v>17.92277336120605</v>
       </c>
       <c r="C49" t="n">
         <v>25.9044017791748</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>17.70256614685059</v>
+        <v>17.70256423950195</v>
       </c>
       <c r="C50" t="n">
         <v>25.40061187744141</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>18.15064811706543</v>
+        <v>18.15064430236816</v>
       </c>
       <c r="C51" t="n">
         <v>26.04354476928711</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.61562538146973</v>
+        <v>17.61562156677246</v>
       </c>
       <c r="C52" t="n">
         <v>25.27586364746094</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.25147438049316</v>
+        <v>17.25146484375</v>
       </c>
       <c r="C53" t="n">
         <v>24.54656791687012</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.03753280639648</v>
+        <v>16.03753089904785</v>
       </c>
       <c r="C54" t="n">
         <v>22.81928825378418</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>15.77450847625732</v>
+        <v>15.77449703216553</v>
       </c>
       <c r="C55" t="n">
         <v>22.44504356384277</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>16.70377159118652</v>
+        <v>16.70377540588379</v>
       </c>
       <c r="C56" t="n">
         <v>23.548583984375</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>16.79225921630859</v>
+        <v>16.79225730895996</v>
       </c>
       <c r="C57" t="n">
         <v>23.67333221435547</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.77924728393555</v>
+        <v>17.77924156188965</v>
       </c>
       <c r="C58" t="n">
         <v>25.06475257873535</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>15.96034145355225</v>
+        <v>15.96034336090088</v>
       </c>
       <c r="C60" t="n">
         <v>22.31549835205078</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>16.44076919555664</v>
+        <v>16.44076728820801</v>
       </c>
       <c r="C61" t="n">
         <v>22.98721885681152</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>15.64092826843262</v>
+        <v>15.6409330368042</v>
       </c>
       <c r="C62" t="n">
         <v>21.66776847839355</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>16.65918159484863</v>
+        <v>16.65918922424316</v>
       </c>
       <c r="C63" t="n">
         <v>23.0783805847168</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98821258544922</v>
+        <v>16.98821640014648</v>
       </c>
       <c r="C64" t="n">
         <v>23.53418922424316</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>18.1949348449707</v>
+        <v>18.19493675231934</v>
       </c>
       <c r="C65" t="n">
         <v>24.96879196166992</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>18.26835441589355</v>
+        <v>18.26835632324219</v>
       </c>
       <c r="C66" t="n">
         <v>25.06954956054688</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>18.39772033691406</v>
+        <v>18.39771842956543</v>
       </c>
       <c r="C67" t="n">
         <v>25.2470760345459</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>18.10627937316895</v>
+        <v>18.10628509521484</v>
       </c>
       <c r="C68" t="n">
         <v>24.62333679199219</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>18.52613639831543</v>
+        <v>18.5261344909668</v>
       </c>
       <c r="C69" t="n">
         <v>25.19429779052734</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.04277610778809</v>
+        <v>18.04277992248535</v>
       </c>
       <c r="C70" t="n">
         <v>24.53697204589844</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.18065071105957</v>
+        <v>19.1806526184082</v>
       </c>
       <c r="C71" t="n">
         <v>25.84682655334473</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.42277145385742</v>
+        <v>19.42278099060059</v>
       </c>
       <c r="C72" t="n">
         <v>26.1730899810791</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.02093887329102</v>
+        <v>20.02094078063965</v>
       </c>
       <c r="C73" t="n">
         <v>26.97915458679199</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>19.44671058654785</v>
+        <v>19.44670295715332</v>
       </c>
       <c r="C74" t="n">
         <v>25.98117065429688</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>20.33016395568848</v>
+        <v>20.33016204833984</v>
       </c>
       <c r="C75" t="n">
         <v>27.16147804260254</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.01086807250977</v>
+        <v>22.0108699798584</v>
       </c>
       <c r="C76" t="n">
         <v>29.40694236755371</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>22.4780216217041</v>
+        <v>22.47801971435547</v>
       </c>
       <c r="C77" t="n">
         <v>29.77638816833496</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.38022041320801</v>
+        <v>22.38022804260254</v>
       </c>
       <c r="C78" t="n">
         <v>29.64684104919434</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>23.35091209411621</v>
+        <v>23.35091400146484</v>
       </c>
       <c r="C79" t="n">
         <v>30.93270683288574</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>23.92426300048828</v>
+        <v>23.92426872253418</v>
       </c>
       <c r="C81" t="n">
         <v>31.44609260559082</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>24.08421325683594</v>
+        <v>24.0842170715332</v>
       </c>
       <c r="C83" t="n">
         <v>31.42690086364746</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.08421325683594</v>
+        <v>24.0842170715332</v>
       </c>
       <c r="C85" t="n">
         <v>31.42690086364746</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.07199478149414</v>
+        <v>26.07199859619141</v>
       </c>
       <c r="C86" t="n">
         <v>33.88000106811523</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>26.00274085998535</v>
+        <v>26.00273323059082</v>
       </c>
       <c r="C87" t="n">
         <v>33.79000091552734</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>27.18014335632324</v>
+        <v>27.18013191223145</v>
       </c>
       <c r="C88" t="n">
         <v>35.31999969482422</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>28.51901245117188</v>
+        <v>28.51901435852051</v>
       </c>
       <c r="C89" t="n">
         <v>36.91999816894531</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>28.32588958740234</v>
+        <v>28.32590293884277</v>
       </c>
       <c r="C90" t="n">
         <v>36.66999816894531</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.94320678710938</v>
+        <v>26.94320487976074</v>
       </c>
       <c r="C91" t="n">
         <v>34.88000106811523</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>28.40947914123535</v>
+        <v>28.40949249267578</v>
       </c>
       <c r="C92" t="n">
         <v>36.63000106811523</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>25.85007476806641</v>
+        <v>25.8500804901123</v>
       </c>
       <c r="C93" t="n">
         <v>33.33000183105469</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>25.74148750305176</v>
+        <v>25.74149322509766</v>
       </c>
       <c r="C94" t="n">
         <v>33.18999862670898</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>28.46758842468262</v>
+        <v>28.46759796142578</v>
       </c>
       <c r="C95" t="n">
         <v>36.54999923706055</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.74493980407715</v>
+        <v>29.74493408203125</v>
       </c>
       <c r="C96" t="n">
         <v>38.18999862670898</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>29.85396766662598</v>
+        <v>29.85397911071777</v>
       </c>
       <c r="C97" t="n">
         <v>38.33000183105469</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>28.7129020690918</v>
+        <v>28.71289825439453</v>
       </c>
       <c r="C98" t="n">
         <v>36.65999984741211</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>31.15654945373535</v>
+        <v>31.15656089782715</v>
       </c>
       <c r="C99" t="n">
         <v>39.77999877929688</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>30.161865234375</v>
+        <v>30.1618709564209</v>
       </c>
       <c r="C100" t="n">
         <v>38.5099983215332</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>31.52280807495117</v>
+        <v>31.5228214263916</v>
       </c>
       <c r="C102" t="n">
         <v>40.0099983215332</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.22404861450195</v>
+        <v>32.22404098510742</v>
       </c>
       <c r="C103" t="n">
         <v>40.90000152587891</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.36321258544922</v>
+        <v>33.36322402954102</v>
       </c>
       <c r="C104" t="n">
         <v>42.11999893188477</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>33.45827865600586</v>
+        <v>33.45828247070312</v>
       </c>
       <c r="C105" t="n">
         <v>42.2400016784668</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.94340515136719</v>
+        <v>32.94340896606445</v>
       </c>
       <c r="C106" t="n">
         <v>41.59000015258789</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>34.71103668212891</v>
+        <v>34.71103286743164</v>
       </c>
       <c r="C107" t="n">
         <v>43.59000015258789</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>35.44363403320312</v>
+        <v>35.44364547729492</v>
       </c>
       <c r="C108" t="n">
         <v>44.5099983215332</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>35.84976959228516</v>
+        <v>35.84976196289062</v>
       </c>
       <c r="C109" t="n">
         <v>45.02000045776367</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>37.92075729370117</v>
+        <v>37.92074966430664</v>
       </c>
       <c r="C111" t="n">
         <v>47.36999893188477</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.08821105957031</v>
+        <v>37.08820724487305</v>
       </c>
       <c r="C112" t="n">
         <v>46.33000183105469</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>37.35036849975586</v>
+        <v>37.35037231445312</v>
       </c>
       <c r="C113" t="n">
         <v>46.41999816894531</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>39.49066162109375</v>
+        <v>39.49066925048828</v>
       </c>
       <c r="C115" t="n">
         <v>49.08000183105469</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>40.98309326171875</v>
+        <v>40.98308563232422</v>
       </c>
       <c r="C116" t="n">
         <v>50.68999862670898</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>36.61716461181641</v>
+        <v>36.6171760559082</v>
       </c>
       <c r="C117" t="n">
         <v>45.29000091552734</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>32.51804733276367</v>
+        <v>32.51803588867188</v>
       </c>
       <c r="C118" t="n">
         <v>40.22000122070312</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>36.43132781982422</v>
+        <v>36.43132019042969</v>
       </c>
       <c r="C119" t="n">
         <v>44.79999923706055</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>36.52890396118164</v>
+        <v>36.52890777587891</v>
       </c>
       <c r="C120" t="n">
         <v>44.91999816894531</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>30.97383117675781</v>
+        <v>30.97383689880371</v>
       </c>
       <c r="C122" t="n">
         <v>37.84999847412109</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>31.70214080810547</v>
+        <v>31.7021541595459</v>
       </c>
       <c r="C123" t="n">
         <v>38.7400016784668</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.02754592895508</v>
+        <v>32.02756500244141</v>
       </c>
       <c r="C125" t="n">
         <v>38.90000152587891</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.62858200073242</v>
+        <v>32.62858581542969</v>
       </c>
       <c r="C126" t="n">
         <v>39.63000106811523</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>32.36511611938477</v>
+        <v>32.3651123046875</v>
       </c>
       <c r="C127" t="n">
         <v>39.31000137329102</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>37.07096862792969</v>
+        <v>37.07097244262695</v>
       </c>
       <c r="C128" t="n">
         <v>44.75</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>34.80944442749023</v>
+        <v>34.80945205688477</v>
       </c>
       <c r="C129" t="n">
         <v>42.02000045776367</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>35.03311157226562</v>
+        <v>35.03313064575195</v>
       </c>
       <c r="C130" t="n">
         <v>42.29000091552734</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>31.73774719238281</v>
+        <v>31.73773002624512</v>
       </c>
       <c r="C132" t="n">
         <v>38.06999969482422</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.0472412109375</v>
+        <v>35.0472526550293</v>
       </c>
       <c r="C134" t="n">
         <v>41.77000045776367</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>37.82451248168945</v>
+        <v>37.82451629638672</v>
       </c>
       <c r="C135" t="n">
         <v>45.08000183105469</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>37.26234436035156</v>
+        <v>37.26235198974609</v>
       </c>
       <c r="C136" t="n">
         <v>44.40999984741211</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.84022903442383</v>
+        <v>36.84024047851562</v>
       </c>
       <c r="C137" t="n">
         <v>43.63999938964844</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>38.54549789428711</v>
+        <v>38.54549407958984</v>
       </c>
       <c r="C138" t="n">
         <v>45.65999984741211</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>41.03582763671875</v>
+        <v>41.03583908081055</v>
       </c>
       <c r="C139" t="n">
         <v>48.61000061035156</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.74677658081055</v>
+        <v>41.74678039550781</v>
       </c>
       <c r="C140" t="n">
         <v>49.18000030517578</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>43.24076843261719</v>
+        <v>43.24077224731445</v>
       </c>
       <c r="C141" t="n">
         <v>50.93999862670898</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>45.29501342773438</v>
+        <v>45.29502868652344</v>
       </c>
       <c r="C142" t="n">
         <v>53.36000061035156</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>46.25869369506836</v>
+        <v>46.25867080688477</v>
       </c>
       <c r="C143" t="n">
         <v>54.22999954223633</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>48.0841178894043</v>
+        <v>48.08412551879883</v>
       </c>
       <c r="C144" t="n">
         <v>56.36999893188477</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>48.68122482299805</v>
+        <v>48.68123245239258</v>
       </c>
       <c r="C145" t="n">
         <v>57.06999969482422</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>53.27661514282227</v>
+        <v>53.2766227722168</v>
       </c>
       <c r="C146" t="n">
         <v>62.15999984741211</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>51.70814514160156</v>
+        <v>51.70814895629883</v>
       </c>
       <c r="C147" t="n">
         <v>60.33000183105469</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.35674667358398</v>
+        <v>51.35673141479492</v>
       </c>
       <c r="C148" t="n">
         <v>59.91999816894531</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>52.99049377441406</v>
+        <v>52.99049758911133</v>
       </c>
       <c r="C150" t="n">
         <v>61.52999877929688</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>52.52544403076172</v>
+        <v>52.52545166015625</v>
       </c>
       <c r="C151" t="n">
         <v>60.9900016784668</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>57.82231521606445</v>
+        <v>57.82229232788086</v>
       </c>
       <c r="C153" t="n">
         <v>66.83999633789062</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>63.46267318725586</v>
+        <v>63.46263885498047</v>
       </c>
       <c r="C154" t="n">
         <v>73.36000061035156</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>59.88418960571289</v>
+        <v>59.88418197631836</v>
       </c>
       <c r="C155" t="n">
         <v>68.94000244140625</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>64.32296752929688</v>
+        <v>64.32297515869141</v>
       </c>
       <c r="C156" t="n">
         <v>74.05000305175781</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>62.82888412475586</v>
+        <v>62.82889556884766</v>
       </c>
       <c r="C157" t="n">
         <v>72.33000183105469</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>63.68746948242188</v>
+        <v>63.68747711181641</v>
       </c>
       <c r="C158" t="n">
         <v>72.98000335693359</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>67.73666381835938</v>
+        <v>67.73664855957031</v>
       </c>
       <c r="C159" t="n">
         <v>77.62000274658203</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>69.76123809814453</v>
+        <v>69.76124572753906</v>
       </c>
       <c r="C160" t="n">
         <v>79.94000244140625</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>73.69190216064453</v>
+        <v>73.69189453125</v>
       </c>
       <c r="C163" t="n">
         <v>84.09999847412109</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>75.04090118408203</v>
+        <v>75.04090881347656</v>
       </c>
       <c r="C165" t="n">
         <v>85.31999969482422</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>73.58967590332031</v>
+        <v>73.58969879150391</v>
       </c>
       <c r="C166" t="n">
         <v>83.66999816894531</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>73.83174896240234</v>
+        <v>73.83173370361328</v>
       </c>
       <c r="C167" t="n">
         <v>83.61000061035156</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>75.45652770996094</v>
+        <v>75.45654296875</v>
       </c>
       <c r="C168" t="n">
         <v>85.44999694824219</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>76.70164489746094</v>
+        <v>76.70165252685547</v>
       </c>
       <c r="C169" t="n">
         <v>86.86000061035156</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>77.27569580078125</v>
+        <v>77.27572631835938</v>
       </c>
       <c r="C170" t="n">
         <v>87.13999938964844</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>81.42149353027344</v>
+        <v>81.42150115966797</v>
       </c>
       <c r="C175" t="n">
         <v>91.43000030517578</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>89.97128295898438</v>
+        <v>89.97126770019531</v>
       </c>
       <c r="C176" t="n">
         <v>100.6399993896484</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>97.86521911621094</v>
+        <v>97.86521148681641</v>
       </c>
       <c r="C177" t="n">
         <v>109.4700012207031</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>97.29306030273438</v>
+        <v>97.29303741455078</v>
       </c>
       <c r="C178" t="n">
         <v>108.8300018310547</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>98.20933532714844</v>
+        <v>98.20932769775391</v>
       </c>
       <c r="C181" t="n">
         <v>109.4899978637695</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>111.3032302856445</v>
+        <v>111.3032379150391</v>
       </c>
       <c r="C182" t="n">
         <v>123.5899963378906</v>
@@ -5245,7 +5245,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>107.8719940185547</v>
+        <v>107.8719863891602</v>
       </c>
       <c r="C183" t="n">
         <v>119.7799987792969</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>107.9260330200195</v>
+        <v>107.9260406494141</v>
       </c>
       <c r="C184" t="n">
         <v>119.8399963378906</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>105.4388885498047</v>
+        <v>105.4388961791992</v>
       </c>
       <c r="C186" t="n">
         <v>116.6500015258789</v>
@@ -5361,7 +5361,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>104.7880859375</v>
+        <v>104.7880935668945</v>
       </c>
       <c r="C187" t="n">
         <v>115.9300003051758</v>
@@ -5390,7 +5390,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>109.7690505981445</v>
+        <v>109.7690582275391</v>
       </c>
       <c r="C188" t="n">
         <v>120.9800033569336</v>
@@ -5477,7 +5477,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>117.397575378418</v>
+        <v>117.3975830078125</v>
       </c>
       <c r="C191" t="n">
         <v>128.8899993896484</v>
@@ -5506,7 +5506,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>114.5557632446289</v>
+        <v>114.5557556152344</v>
       </c>
       <c r="C192" t="n">
         <v>125.7699966430664</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>128.1909942626953</v>
+        <v>128.1909332275391</v>
       </c>
       <c r="C193" t="n">
         <v>140.7400054931641</v>
@@ -5593,7 +5593,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>110.2524948120117</v>
+        <v>110.2524795532227</v>
       </c>
       <c r="C195" t="n">
         <v>120.620002746582</v>
@@ -5651,7 +5651,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>104.1579666137695</v>
+        <v>104.1579742431641</v>
       </c>
       <c r="C197" t="n">
         <v>113.5</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>107.7920150756836</v>
+        <v>107.7920227050781</v>
       </c>
       <c r="C198" t="n">
         <v>117.4599990844727</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>100.3254623413086</v>
+        <v>100.3254776000977</v>
       </c>
       <c r="C200" t="n">
         <v>108.8399963378906</v>
@@ -5767,7 +5767,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>94.61972808837891</v>
+        <v>94.61972045898438</v>
       </c>
       <c r="C201" t="n">
         <v>102.6500015258789</v>
@@ -5883,7 +5883,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>101.6786804199219</v>
+        <v>101.6786727905273</v>
       </c>
       <c r="C205" t="n">
         <v>109.7900009155273</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>102.8460845947266</v>
+        <v>102.846076965332</v>
       </c>
       <c r="C206" t="n">
         <v>110.5500030517578</v>
@@ -5941,7 +5941,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>94.63140106201172</v>
+        <v>94.63141632080078</v>
       </c>
       <c r="C207" t="n">
         <v>101.7200012207031</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>94.20347595214844</v>
+        <v>94.20346832275391</v>
       </c>
       <c r="C208" t="n">
         <v>101.2600021362305</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>103.2852630615234</v>
+        <v>103.2852554321289</v>
       </c>
       <c r="C209" t="n">
         <v>110.4700012207031</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>95.36611938476562</v>
+        <v>95.36612701416016</v>
       </c>
       <c r="C210" t="n">
         <v>102</v>
@@ -6057,7 +6057,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>101.9295501708984</v>
+        <v>101.929557800293</v>
       </c>
       <c r="C211" t="n">
         <v>109.0199966430664</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>96.66900634765625</v>
+        <v>96.66899871826172</v>
       </c>
       <c r="C213" t="n">
         <v>102.9000015258789</v>
@@ -6144,7 +6144,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>90.9853515625</v>
+        <v>90.98534393310547</v>
       </c>
       <c r="C214" t="n">
         <v>96.84999847412109</v>
@@ -6173,7 +6173,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>89.31632995605469</v>
+        <v>89.31633758544922</v>
       </c>
       <c r="C215" t="n">
         <v>94.55000305175781</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>98.51718902587891</v>
+        <v>98.51717376708984</v>
       </c>
       <c r="C216" t="n">
         <v>104.2900009155273</v>
@@ -6231,7 +6231,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>103.9772491455078</v>
+        <v>103.9772567749023</v>
       </c>
       <c r="C217" t="n">
         <v>110.0699996948242</v>
@@ -6289,7 +6289,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>112.6142883300781</v>
+        <v>112.6142730712891</v>
       </c>
       <c r="C219" t="n">
         <v>118.6399993896484</v>
@@ -6318,7 +6318,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>107.8872222900391</v>
+        <v>107.8872146606445</v>
       </c>
       <c r="C220" t="n">
         <v>113.6600036621094</v>
@@ -6376,7 +6376,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>97.48085021972656</v>
+        <v>97.48084259033203</v>
       </c>
       <c r="C222" t="n">
         <v>102.1900024414062</v>
@@ -6405,7 +6405,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>99.12158203125</v>
+        <v>99.12158966064453</v>
       </c>
       <c r="C223" t="n">
         <v>103.9100036621094</v>
@@ -6434,7 +6434,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>101.5941772460938</v>
+        <v>101.5941848754883</v>
       </c>
       <c r="C224" t="n">
         <v>105.9400024414062</v>
@@ -6463,7 +6463,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>108.6234817504883</v>
+        <v>108.6234741210938</v>
       </c>
       <c r="C225" t="n">
         <v>113.2699966430664</v>
@@ -6579,7 +6579,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>108.9812698364258</v>
+        <v>108.9812622070312</v>
       </c>
       <c r="C229" t="n">
         <v>113.1100006103516</v>
@@ -6608,7 +6608,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>123.9071273803711</v>
+        <v>123.9071350097656</v>
       </c>
       <c r="C230" t="n">
         <v>127.9300003051758</v>
@@ -6637,7 +6637,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>133.670166015625</v>
+        <v>133.6701507568359</v>
       </c>
       <c r="C231" t="n">
         <v>138.0099945068359</v>
@@ -6666,7 +6666,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>128.4786834716797</v>
+        <v>128.4786987304688</v>
       </c>
       <c r="C232" t="n">
         <v>132.6499938964844</v>
@@ -6695,7 +6695,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>127.2250671386719</v>
+        <v>127.2250595092773</v>
       </c>
       <c r="C233" t="n">
         <v>130.75</v>
@@ -6811,7 +6811,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>129.6630096435547</v>
+        <v>129.6629943847656</v>
       </c>
       <c r="C237" t="n">
         <v>132.6600036621094</v>
@@ -6927,7 +6927,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>123.0040588378906</v>
+        <v>123.0040512084961</v>
       </c>
       <c r="C241" t="n">
         <v>125.2900009155273</v>
@@ -6956,7 +6956,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>107.8493499755859</v>
+        <v>107.8493576049805</v>
       </c>
       <c r="C242" t="n">
         <v>109.3000030517578</v>
